--- a/output/stock_quant_scores/RIO_income_df.xlsx
+++ b/output/stock_quant_scores/RIO_income_df.xlsx
@@ -1332,7 +1332,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>31429000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1344,11 +1346,15 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>13.047</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>21115000000</v>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1374,9 +1380,13 @@
         <v>3083000000</v>
       </c>
       <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>44934000000</v>
+      </c>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>63495000000</v>
+      </c>
       <c r="AZ6" t="inlineStr"/>
     </row>
   </sheetData>
